--- a/data/trans_orig/IP25A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>27378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43338</t>
+          <t>43789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30902</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47632</t>
+          <t>47203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61785</t>
+          <t>63161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85197</t>
+          <t>87300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>81708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98187</t>
+          <t>98119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88792</t>
+          <t>89221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105522</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176724</t>
+          <t>174621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200136</t>
+          <t>198760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62642</t>
+          <t>61728</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82058</t>
+          <t>82266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61513</t>
+          <t>61589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129030</t>
+          <t>127887</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156713</t>
+          <t>159776</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90435</t>
+          <t>90227</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109851</t>
+          <t>110765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121899</t>
+          <t>121823</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199192</t>
+          <t>196129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>226875</t>
+          <t>228018</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>36316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53767</t>
+          <t>52805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>44038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61060</t>
+          <t>61861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86119</t>
+          <t>85831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110742</t>
+          <t>109492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68539</t>
+          <t>69501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85594</t>
+          <t>85990</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71053</t>
+          <t>70252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88821</t>
+          <t>88075</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>144927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168300</t>
+          <t>168588</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,26%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60894</t>
+          <t>59988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84351</t>
+          <t>82504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68145</t>
+          <t>68269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88379</t>
+          <t>90376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134814</t>
+          <t>133751</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165135</t>
+          <t>166739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>109104</t>
+          <t>110951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132561</t>
+          <t>133467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91620</t>
+          <t>89623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111854</t>
+          <t>111730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208319</t>
+          <t>206715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238640</t>
+          <t>239703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>204283</t>
+          <t>203162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241902</t>
+          <t>242286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>221272</t>
+          <t>220854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>262514</t>
+          <t>261072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436116</t>
+          <t>438107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>490173</t>
+          <t>491761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371848</t>
+          <t>371464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409467</t>
+          <t>410588</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>369435</t>
+          <t>370877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410677</t>
+          <t>411095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>755526</t>
+          <t>753938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>809583</t>
+          <t>807592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>37124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55191</t>
+          <t>55720</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>40852</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60585</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84413</t>
+          <t>84075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110740</t>
+          <t>110781</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73181</t>
+          <t>72652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90844</t>
+          <t>91248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80533</t>
+          <t>80426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100364</t>
+          <t>100266</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158751</t>
+          <t>158710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185078</t>
+          <t>185416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,8%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53901</t>
+          <t>54137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73764</t>
+          <t>74210</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60422</t>
+          <t>60133</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>81758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118797</t>
+          <t>119768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150235</t>
+          <t>149908</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112293</t>
+          <t>111847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132156</t>
+          <t>131920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118257</t>
+          <t>119009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140345</t>
+          <t>140634</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236589</t>
+          <t>236916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>268027</t>
+          <t>267056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32919</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50131</t>
+          <t>49950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42414</t>
+          <t>43538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61234</t>
+          <t>62872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81333</t>
+          <t>82611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106552</t>
+          <t>106520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81197</t>
+          <t>81378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98409</t>
+          <t>98217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88049</t>
+          <t>86411</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106869</t>
+          <t>105745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174059</t>
+          <t>174091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199278</t>
+          <t>198000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60789</t>
+          <t>60854</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83487</t>
+          <t>83934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63556</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85691</t>
+          <t>86443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130976</t>
+          <t>132607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163755</t>
+          <t>163235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102759</t>
+          <t>102312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>125457</t>
+          <t>125392</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106182</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128317</t>
+          <t>128187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214364</t>
+          <t>214884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>247143</t>
+          <t>245512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205233</t>
+          <t>204560</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>228621</t>
+          <t>228526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>267905</t>
+          <t>269667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>445925</t>
+          <t>443391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>503374</t>
+          <t>498740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385389</t>
+          <t>387354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>426770</t>
+          <t>427443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>415137</t>
+          <t>413375</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454421</t>
+          <t>454516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>811671</t>
+          <t>816305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>869120</t>
+          <t>871654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48653</t>
+          <t>47639</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66601</t>
+          <t>66535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>59723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79389</t>
+          <t>78797</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113076</t>
+          <t>114168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139840</t>
+          <t>140927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>50770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68652</t>
+          <t>69666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55254</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75153</t>
+          <t>74920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112107</t>
+          <t>111020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138871</t>
+          <t>137779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>63645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82969</t>
+          <t>83495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>71805</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94932</t>
+          <t>95158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>140934</t>
+          <t>141482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172074</t>
+          <t>172237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,22%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102381</t>
+          <t>101855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122971</t>
+          <t>121705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109177</t>
+          <t>108951</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132304</t>
+          <t>130995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>217385</t>
+          <t>217222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248525</t>
+          <t>247977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>57686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75597</t>
+          <t>77101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54818</t>
+          <t>55342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75400</t>
+          <t>75654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117240</t>
+          <t>117252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144394</t>
+          <t>143966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,06%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67380</t>
+          <t>65876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85591</t>
+          <t>85291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81181</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>101239</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155164</t>
+          <t>155592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182318</t>
+          <t>182306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>69615</t>
+          <t>70416</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>92925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77830</t>
+          <t>78242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101006</t>
+          <t>99555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>156104</t>
+          <t>155581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187027</t>
+          <t>188535</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107126</t>
+          <t>106325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78718</t>
+          <t>80169</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101894</t>
+          <t>101482</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169437</t>
+          <t>167929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200360</t>
+          <t>200883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,35%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>259939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300004</t>
+          <t>298730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285822</t>
+          <t>284906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>329572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>556494</t>
+          <t>559183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>617007</t>
+          <t>616350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>322368</t>
+          <t>323642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>362433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346857</t>
+          <t>345484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>389234</t>
+          <t>390150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>680421</t>
+          <t>681078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>740934</t>
+          <t>738245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Habitat-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30329</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46985</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35066</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27378</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43789</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26749</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44112</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>30489</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47203</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63161</t>
+          <t>63653</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87300</t>
+          <t>86407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97635</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>89439</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>106095</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90431</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>81708</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>98119</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>81385</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>98748</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>65,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,18%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97635</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>89221</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>105935</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>174621</t>
+          <t>175514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198760</t>
+          <t>198268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,7%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>136424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>136424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>136424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>125497</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>125497</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>125497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>136424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>136424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>136424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71837</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61322</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>83038</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>72011</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>61728</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>82266</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>62143</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>82769</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>41,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>71837</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>61589</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81989</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127887</t>
+          <t>129880</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159776</t>
+          <t>159230</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111575</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100374</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>122090</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>66,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100482</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90227</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110765</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89724</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>110350</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>58,25%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>64,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111575</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>101423</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121823</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>60,83%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196129</t>
+          <t>196675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228018</t>
+          <t>226025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>183412</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>183412</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>183412</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>172493</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>172493</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>172493</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>183412</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>183412</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>183412</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52455</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>43018</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61390</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>44505</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36316</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>52805</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>36561</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>52976</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>36,39%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>52455</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>44038</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>61861</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,7%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85831</t>
+          <t>84581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109492</t>
+          <t>108276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>79658</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70723</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>89095</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>53,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77801</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>69501</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85990</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>69330</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85745</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>63,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>79658</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70252</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>88075</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>60,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144927</t>
+          <t>146143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168588</t>
+          <t>169838</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132113</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132113</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132113</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>122306</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>122306</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>122306</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132113</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132113</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132113</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>78389</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>68595</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>88895</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>43,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>71484</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>59988</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82504</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>60711</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>83314</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>36,95%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>78389</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>68269</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>90376</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>43,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133751</t>
+          <t>136280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166739</t>
+          <t>165728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>101610</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>91104</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>111404</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>56,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>121971</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>110951</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>133467</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>110141</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>132744</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>63,05%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>101610</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>89623</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>111730</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206715</t>
+          <t>207726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239703</t>
+          <t>237174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179999</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179999</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179999</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193455</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193455</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193455</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179999</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179999</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179999</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>222136</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>262108</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>38,21%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>223065</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>203162</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>242286</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>203647</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>241490</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>241471</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>220854</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>261072</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>438107</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>491761</t>
+          <t>492547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>390478</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>369841</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>409813</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>61,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>390685</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>371464</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>410588</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>372260</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>410103</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>63,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>66,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>390478</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>370877</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>411095</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>61,79%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>753938</t>
+          <t>753152</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807592</t>
+          <t>807690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>631949</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>631949</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>631949</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>613750</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>631949</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>631949</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>631949</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2484,13 +2484,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50646</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40644</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60225</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>46498</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>37124</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>55720</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>37673</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>55582</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>43,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>50646</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>40852</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>60692</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>84075</t>
+          <t>84396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110781</t>
+          <t>111132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>90472</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>80893</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>100474</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>64,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>81874</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72652</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91248</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72790</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>90699</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>56,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>90472</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>80426</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>100266</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>64,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158710</t>
+          <t>158359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185416</t>
+          <t>185095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,68%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>141118</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141118</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>141118</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>128372</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>128372</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>128372</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>141118</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>141118</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>141118</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71031</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>61083</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82729</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>63985</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54137</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>74210</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>53878</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>73762</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>71031</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>60133</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81758</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,38%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119768</t>
+          <t>120445</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>149908</t>
+          <t>151188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -3130,67 +3130,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>129736</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>118038</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>139684</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>122072</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111847</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>131920</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>112295</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>132179</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>70,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>129736</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>119009</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>140634</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,62%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>236916</t>
+          <t>235636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267056</t>
+          <t>266379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>200767</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>200767</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>200767</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>186057</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>186057</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>186057</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>200767</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>200767</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>200767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51908</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>42658</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>61159</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>41270</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33111</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>49950</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>33844</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>50051</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>51908</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>43538</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>62872</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82611</t>
+          <t>80513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106520</t>
+          <t>105945</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,76%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>97375</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>88124</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106625</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>90058</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81378</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>98217</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>81277</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>97484</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>68,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>97375</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86411</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>105745</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>65,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174091</t>
+          <t>174666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198000</t>
+          <t>200098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149283</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149283</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149283</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>131328</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>131328</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>131328</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149283</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149283</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74644</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>63268</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>87372</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>45,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>72645</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>60854</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83934</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>61043</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>84989</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>39,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,67%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>45,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>74644</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>63686</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>86443</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132607</t>
+          <t>132322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163235</t>
+          <t>164048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>117229</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>104501</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>128605</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>67,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>113601</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>102312</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>125392</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>101257</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>125203</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>54,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>117229</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>105430</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>128187</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214884</t>
+          <t>214071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245512</t>
+          <t>245797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,01%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>191873</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>191873</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>191873</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>186246</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>186246</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>186246</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>191873</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>191873</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>191873</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>228270</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>270779</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>224398</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>204560</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>244649</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>204349</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>246544</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>248229</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>228526</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>269667</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>443391</t>
+          <t>445637</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>498740</t>
+          <t>501424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>434813</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>454772</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>591</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>407605</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>387354</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>427443</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>385459</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>427654</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>434813</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>413375</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>454516</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>63,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>816305</t>
+          <t>813621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>871654</t>
+          <t>869408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>683042</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>683042</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>683042</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>632003</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>632003</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>632003</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>683042</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>683042</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>683042</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,13 +4431,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>69553</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>60149</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>80162</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>59,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>57703</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>47639</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66535</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>48204</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66677</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,19%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>69553</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>59723</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>78797</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114168</t>
+          <t>113342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140927</t>
+          <t>141626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65090</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54481</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74494</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>48,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>40,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59602</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50770</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69666</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50628</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69101</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,81%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>43,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65090</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55846</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74920</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>48,34%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111020</t>
+          <t>110321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137779</t>
+          <t>138605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,01%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>134643</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>134643</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>134643</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>117305</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>117305</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>117305</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>134643</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>134643</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>134643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>83906</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71863</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>94690</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,39%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>72661</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>63645</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>83495</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>61580</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>83273</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>39,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>83906</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>73114</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>95158</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>41,11%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141482</t>
+          <t>140212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172237</t>
+          <t>171931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -5077,67 +5077,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>120203</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>109419</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>132246</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>112689</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>101855</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>121705</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>102077</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>123770</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>60,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>120203</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>108951</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>130995</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>58,89%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>217222</t>
+          <t>217528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247977</t>
+          <t>249247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>204109</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204109</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204109</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185350</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185350</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185350</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>204109</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>204109</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>204109</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64728</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55105</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>74737</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>47,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66182</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57686</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77101</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>57600</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76575</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>46,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>64728</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>55342</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>75654</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>41,34%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117252</t>
+          <t>116567</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143966</t>
+          <t>144714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91853</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81844</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101476</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>52,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>76795</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65876</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85291</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66402</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85377</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>53,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>91853</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>80927</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>101239</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>58,66%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155592</t>
+          <t>154844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182306</t>
+          <t>182991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156581</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156581</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156581</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>142977</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>142977</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>142977</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156581</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156581</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156581</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>88876</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>78591</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>99485</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>82489</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>70416</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>92925</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>70550</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>93720</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>46,67%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>88876</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>78242</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>99555</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>49,45%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>155581</t>
+          <t>155324</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188535</t>
+          <t>186624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,35%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>90848</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80239</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>101133</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>50,55%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>94252</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83816</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106325</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>83021</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>106191</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>53,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>90848</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>80169</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>101482</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>50,55%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167929</t>
+          <t>169840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200883</t>
+          <t>201140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179724</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179724</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179724</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>238</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>176741</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>176741</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>176741</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179724</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179724</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179724</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>285940</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>329699</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>48,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>412</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>279034</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>259939</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>298730</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>260763</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>300181</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,83%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>307063</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>284906</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>329572</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>559183</t>
+          <t>558745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>616350</t>
+          <t>613965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>367993</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>345357</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>389116</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>51,16%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>343338</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>323642</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>362433</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>322191</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>361609</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>55,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>52,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,23%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>367993</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>345484</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>390150</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>54,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>681078</t>
+          <t>683463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>738245</t>
+          <t>738683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>622372</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>622372</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>622372</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
